--- a/demo_data/doctor_availability.xlsx
+++ b/demo_data/doctor_availability.xlsx
@@ -483,7 +483,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="3">
@@ -499,12 +499,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -516,7 +516,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
@@ -532,7 +532,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -549,7 +549,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5">
@@ -565,12 +565,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -582,7 +582,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6">
@@ -598,12 +598,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -615,7 +615,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
@@ -631,12 +631,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -648,7 +648,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -664,12 +664,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -681,7 +681,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9">
@@ -697,12 +697,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -714,7 +714,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
@@ -730,7 +730,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -780,7 +780,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12">
@@ -796,12 +796,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -813,7 +813,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="13">
@@ -834,7 +834,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="14">
@@ -862,12 +862,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -912,7 +912,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16">
@@ -928,12 +928,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -945,7 +945,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17">
@@ -961,12 +961,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -978,7 +978,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="18">
@@ -994,12 +994,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1011,7 +1011,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="19">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1044,7 +1044,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1110,7 +1110,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
